--- a/cerdanyola_offer_candidates_500_600k.xlsx
+++ b/cerdanyola_offer_candidates_500_600k.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,30 +481,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>reactivation_events</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>budget_fit_score</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>quality_score</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>negotiation_model_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>final_score</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>final_score_reactivated</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>why_it_ranks</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
@@ -513,33 +518,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-53321-Promo-75-110659374</t>
+          <t>idealista_111105534</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Piso en calle De la Ciència en Serraparera, Cerdanyola del Vallès</t>
+          <t>Dúplex en Calle de Pompeu Fabra, 17, Caneletes-Turonet, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>600000</v>
+        <v>490000</v>
       </c>
       <c r="E2" t="n">
-        <v>161</v>
+        <v>107</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G2" t="n">
         <v>3</v>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -548,32 +551,35 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.744</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.643</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.995</v>
+        <v>0.5021354636540157</v>
       </c>
       <c r="N2" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.3335192820180348</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.540069998968318</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-75-110659374</t>
+          <t>within target band, 1 reactivation(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111105534/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-58132-Promo-33-111333235</t>
+          <t>yaencontre_inmueble-58132-Promo-33-111333234</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -587,7 +593,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>533000</v>
+        <v>524000</v>
       </c>
       <c r="E3" t="n">
         <v>144</v>
@@ -599,7 +605,7 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -608,32 +614,35 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.729</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.604</v>
+        <v>0.48</v>
       </c>
       <c r="M3" t="n">
-        <v>0.999</v>
+        <v>0.619436262882465</v>
       </c>
       <c r="N3" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="O3" t="inlineStr">
+        <v>0.4629377630894386</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5361985573544278</v>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-58132-Promo-33-111333235</t>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-58132-Promo-33-111333234</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-53321-Promo-77-111501478</t>
+          <t>yaencontre_inmueble-86283-Promo-1-110755512</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -647,19 +656,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>530000</v>
+        <v>503000</v>
       </c>
       <c r="E4" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -668,32 +677,35 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.706</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.598</v>
+        <v>0.585</v>
       </c>
       <c r="M4" t="n">
-        <v>0.999</v>
+        <v>0.5357294605990124</v>
       </c>
       <c r="N4" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="O4" t="inlineStr">
+        <v>0.4639111598927155</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.5358377099158693</v>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-77-111501478</t>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-110755512</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-53321-Promo-75-111142454</t>
+          <t>yaencontre_inmueble-53321-Promo-77-111572440</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -703,23 +715,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Piso en calle De la Ciència en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>613000</v>
+        <v>498000</v>
       </c>
       <c r="E5" t="n">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -728,32 +740,35 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.642</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.643</v>
+        <v>0.59</v>
       </c>
       <c r="M5" t="n">
-        <v>0.995</v>
+        <v>0.5282274155469794</v>
       </c>
       <c r="N5" t="n">
-        <v>0.713</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.4633393544633987</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.534251080179618</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-75-111142454</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-77-111572440</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-53321-Promo-75-111411842</t>
+          <t>yaencontre_inmueble-58132-Promo-33-111333235</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -763,23 +778,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Piso en calle De la Ciència en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en calle Còrdova en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>616000</v>
+        <v>533000</v>
       </c>
       <c r="E6" t="n">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -788,32 +803,35 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.619</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.646</v>
+        <v>0.435</v>
       </c>
       <c r="M6" t="n">
-        <v>0.995</v>
+        <v>0.6199023494338322</v>
       </c>
       <c r="N6" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.4610603561790398</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5212627026694422</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-75-111411842</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-58132-Promo-33-111333235</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-58132-Promo-33-111333234</t>
+          <t>yaencontre_inmueble-53321-Promo-77-111718387</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -823,23 +841,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Piso en calle Còrdova en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>524000</v>
+        <v>494000</v>
       </c>
       <c r="E7" t="n">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02</v>
+        <v>33.23884337148149</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -848,25 +866,28 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.659</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.604</v>
+        <v>0.57</v>
       </c>
       <c r="M7" t="n">
-        <v>0.998</v>
+        <v>0.525761096031756</v>
       </c>
       <c r="N7" t="n">
-        <v>0.702</v>
-      </c>
-      <c r="O7" t="inlineStr">
+        <v>0.4254870170722213</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5209373753745474</v>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-58132-Promo-33-111333234</t>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-77-111718387</t>
         </is>
       </c>
     </row>
@@ -899,7 +920,7 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -908,23 +929,26 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6820000000000001</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.578</v>
+        <v>0.465</v>
       </c>
       <c r="M8" t="n">
-        <v>0.998</v>
+        <v>0.5941263812439878</v>
       </c>
       <c r="N8" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="O8" t="inlineStr">
+        <v>0.4609323615336482</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5203175968328988</v>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>https://www.yaencontre.com/venta/piso/inmueble-58132-Promo-33-111333124</t>
         </is>
@@ -933,7 +957,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-86283-Promo-1-110324575</t>
+          <t>yaencontre_inmueble-53321-Promo-77-111718398</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -947,19 +971,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>589000</v>
+        <v>530000</v>
       </c>
       <c r="E9" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02</v>
+        <v>33.23884337148149</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -968,32 +992,35 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.779</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.498</v>
+        <v>0.45</v>
       </c>
       <c r="M9" t="n">
-        <v>0.998</v>
+        <v>0.6141191540698129</v>
       </c>
       <c r="N9" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="O9" t="inlineStr">
+        <v>0.424256761893792</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.518263221473767</v>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-110324575</t>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-77-111718398</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-52952-110627382</t>
+          <t>yaencontre_inmueble-58132-Promo-33-111333224</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1003,23 +1030,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Piso en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en calle Còrdova en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>529000</v>
+        <v>514000</v>
       </c>
       <c r="E10" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -1028,32 +1055,35 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.698</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.544</v>
+        <v>0.5299999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.998</v>
+        <v>0.5310150133984173</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="O10" t="inlineStr">
+        <v>0.4620111746968288</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.5154226443122363</v>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-52952-110627382</t>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-58132-Promo-33-111333224</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-9100-111526446</t>
+          <t>yaencontre_inmueble-86283-Promo-1-110755511</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1063,23 +1093,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Piso en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>529000</v>
+        <v>521000</v>
       </c>
       <c r="E11" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1088,58 +1118,59 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.698</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.544</v>
+        <v>0.4949999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.998</v>
+        <v>0.5321260921534372</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="O11" t="inlineStr">
+        <v>0.4611132280177029</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.5042046053874758</v>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-9100-111526446</t>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-110755511</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-56945-110586775</t>
+          <t>idealista_111357087</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Piso en Serraparera, Cerdanyola del Vallès</t>
+          <t>Dúplex en Calle de Sant Ramon, 197, Sant Ramón, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>529000</v>
+        <v>473000</v>
       </c>
       <c r="E12" t="n">
-        <v>118</v>
+        <v>190</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -1148,32 +1179,35 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.698</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.544</v>
+        <v>0.465</v>
       </c>
       <c r="M12" t="n">
-        <v>0.998</v>
+        <v>0.5904095007473821</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="O12" t="inlineStr">
+        <v>0.3569720523415487</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.5031624606455095</v>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-56945-110586775</t>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111357087/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-44301-111521058</t>
+          <t>yaencontre_inmueble-9100-111526446</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1183,23 +1217,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dúplex en Guiera - Montflorit, Cerdanyola del Vallès</t>
+          <t>Piso en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>515000</v>
+        <v>529000</v>
       </c>
       <c r="E13" t="n">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -1208,32 +1242,35 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.588</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.626</v>
+        <v>0.455</v>
       </c>
       <c r="M13" t="n">
-        <v>0.995</v>
+        <v>0.5617154435909398</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="O13" t="inlineStr">
+        <v>0.4587348094794174</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.5030753702104841</v>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-44301-111521058</t>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-9100-111526446</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-54914-110632840</t>
+          <t>yaencontre_inmueble-52952-110627382</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1250,7 +1287,7 @@
         <v>529000</v>
       </c>
       <c r="E14" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="F14" t="n">
         <v>4</v>
@@ -1259,7 +1296,7 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -1268,32 +1305,35 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.698</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.488</v>
+        <v>0.455</v>
       </c>
       <c r="M14" t="n">
-        <v>0.996</v>
+        <v>0.5617154435909398</v>
       </c>
       <c r="N14" t="n">
-        <v>0.663</v>
-      </c>
-      <c r="O14" t="inlineStr">
+        <v>0.4587348094794174</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5030753702104841</v>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-54914-110632840</t>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-52952-110627382</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-53321-Promo-75-111385063</t>
+          <t>yaencontre_inmueble-56945-110586775</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1303,23 +1343,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Piso en calle De la Ciència en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>525000</v>
+        <v>529000</v>
       </c>
       <c r="E15" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -1328,32 +1368,35 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.666</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.492</v>
+        <v>0.455</v>
       </c>
       <c r="M15" t="n">
-        <v>0.998</v>
+        <v>0.5617154435909398</v>
       </c>
       <c r="N15" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="O15" t="inlineStr">
+        <v>0.4587348094794174</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.5030753702104841</v>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-75-111385063</t>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-56945-110586775</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-86283-Promo-1-110755511</t>
+          <t>yaencontre_inmueble-90989-111207597</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1363,14 +1406,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en rambla De Montserrat en Catalunya - Fontetes, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>521000</v>
+        <v>500000</v>
       </c>
       <c r="E16" t="n">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
@@ -1379,7 +1422,7 @@
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -1388,32 +1431,35 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.635</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.515</v>
+        <v>0.6</v>
       </c>
       <c r="M16" t="n">
-        <v>0.998</v>
+        <v>0.4104339009430577</v>
       </c>
       <c r="N16" t="n">
-        <v>0.653</v>
-      </c>
-      <c r="O16" t="inlineStr">
+        <v>0.478631516833925</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.4903716284015497</v>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-110755511</t>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-90989-111207597</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-58132-Promo-33-111333224</t>
+          <t>yaencontre_inmueble-86283-Promo-1-109242345</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1423,14 +1469,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Piso en calle Còrdova en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>514000</v>
+        <v>485000</v>
       </c>
       <c r="E17" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F17" t="n">
         <v>3</v>
@@ -1439,7 +1485,7 @@
         <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02</v>
+        <v>18.17630864925926</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -1448,32 +1494,35 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.513</v>
+        <v>0.525</v>
       </c>
       <c r="M17" t="n">
-        <v>0.998</v>
+        <v>0.5375931185021788</v>
       </c>
       <c r="N17" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="O17" t="inlineStr">
+        <v>0.2800270370449184</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.4892378278080296</v>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-58132-Promo-33-111333224</t>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-109242345</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-86283-Promo-1-110755547</t>
+          <t>yaencontre_inmueble-86283-Promo-1-110755540</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1487,7 +1536,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>516000</v>
+        <v>487000</v>
       </c>
       <c r="E18" t="n">
         <v>120</v>
@@ -1499,7 +1548,7 @@
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -1508,32 +1557,35 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.596</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5</v>
+        <v>0.5349999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>0.998</v>
+        <v>0.4498696783672717</v>
       </c>
       <c r="N18" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="O18" t="inlineStr">
+        <v>0.4800000164959801</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.4856899298690279</v>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-110755547</t>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-110755540</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-53982-110692215</t>
+          <t>yaencontre_inmueble-53321-Promo-75-111915704</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1543,23 +1595,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Piso en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en calle De la Ciència en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>515000</v>
+        <v>509000</v>
       </c>
       <c r="E19" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0.02</v>
+        <v>11.0395956862963</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -1568,32 +1620,35 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.588</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.446</v>
+        <v>0.555</v>
       </c>
       <c r="M19" t="n">
-        <v>0.996</v>
+        <v>0.5283754534883202</v>
       </c>
       <c r="N19" t="n">
-        <v>0.606</v>
-      </c>
-      <c r="O19" t="inlineStr">
+        <v>0.2134130385363624</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.4852743087259256</v>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-53982-110692215</t>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-75-111915704</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-86283-Promo-1-110755512</t>
+          <t>yaencontre_inmueble-53321-Promo-77-111718386</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1607,10 +1662,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>503000</v>
+        <v>468000</v>
       </c>
       <c r="E20" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F20" t="n">
         <v>3</v>
@@ -1619,7 +1674,7 @@
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0.02</v>
+        <v>33.23884337148149</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -1628,58 +1683,59 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.494</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.518</v>
+        <v>0.44</v>
       </c>
       <c r="M20" t="n">
-        <v>0.998</v>
+        <v>0.537260191973155</v>
       </c>
       <c r="N20" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="O20" t="inlineStr">
+        <v>0.4200198493576626</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.4820469205127512</v>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-110755512</t>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-77-111718386</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-53321-Promo-77-111572440</t>
+          <t>idealista_110755512</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>498000</v>
+        <v>503000</v>
       </c>
       <c r="E21" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F21" t="n">
         <v>3</v>
       </c>
-      <c r="G21" t="n">
-        <v>2</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -1688,58 +1744,59 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.454</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.51</v>
+        <v>0.585</v>
       </c>
       <c r="M21" t="n">
-        <v>0.998</v>
+        <v>0.4357137620118853</v>
       </c>
       <c r="N21" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="O21" t="inlineStr">
+        <v>0.3569792045801342</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.4777913232123887</v>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-77-111572440</t>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110755512/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-53321-Promo-77-111597228</t>
+          <t>idealista_111572440</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en Calle de Creu Casas i Sicart, 1, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>494000</v>
+        <v>498000</v>
       </c>
       <c r="E22" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" t="n">
-        <v>2</v>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -1748,58 +1805,59 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.423</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.508</v>
+        <v>0.59</v>
       </c>
       <c r="M22" t="n">
-        <v>0.999</v>
+        <v>0.4297815756725681</v>
       </c>
       <c r="N22" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="O22" t="inlineStr">
+        <v>0.3565336935275896</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.4768829782919938</v>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-77-111597228</t>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111572440/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-90989-111206916</t>
+          <t>idealista_110926853</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Piso en rambla De Montserrat en Catalunya - Fontetes, Cerdanyola del Vallès</t>
+          <t>Casa o chalet en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>625000</v>
+        <v>495000</v>
       </c>
       <c r="E23" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -1808,58 +1866,59 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.548</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.384</v>
+        <v>0.575</v>
       </c>
       <c r="M23" t="n">
-        <v>0.996</v>
+        <v>0.4410686512120346</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.3536322835645281</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.4762383385241106</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-90989-111206916</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110926853/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-53321-Promo-77-111531447</t>
+          <t>idealista_111009273</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
+          <t>Chalet adosado en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>488000</v>
+        <v>495000</v>
       </c>
       <c r="E24" t="n">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -1868,58 +1927,59 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.376</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.51</v>
+        <v>0.575</v>
       </c>
       <c r="M24" t="n">
-        <v>0.999</v>
+        <v>0.4410686512120346</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="O24" t="inlineStr">
+        <v>0.3536322830604469</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.4762383384484984</v>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-77-111531447</t>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111009273/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-86283-Promo-1-111587545</t>
+          <t>idealista_110912717</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
+          <t>Casa o chalet en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>486000</v>
+        <v>495000</v>
       </c>
       <c r="E25" t="n">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -1928,58 +1988,59 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.519</v>
+        <v>0.575</v>
       </c>
       <c r="M25" t="n">
-        <v>0.999</v>
+        <v>0.4410686512120346</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="O25" t="inlineStr">
+        <v>0.3536322830604469</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.4762383384484984</v>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-111587545</t>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110912717/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-49059-111202237</t>
+          <t>idealista_111333234</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ático en Altamira - Canaletes, Cerdanyola del Vallès</t>
+          <t>Piso en Còrdova s/n, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>476000</v>
+        <v>524000</v>
       </c>
       <c r="E26" t="n">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
       </c>
-      <c r="G26" t="n">
-        <v>2</v>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -1988,32 +2049,35 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.281</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="M26" t="n">
-        <v>0.997</v>
+        <v>0.5121992142168449</v>
       </c>
       <c r="N26" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="O26" t="inlineStr">
+        <v>0.3560272401802897</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.4751224184784951</v>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-49059-111202237</t>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111333234/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-90989-111207597</t>
+          <t>yaencontre_inmueble-90989-111207233</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2027,7 +2091,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>500000</v>
+        <v>490000</v>
       </c>
       <c r="E27" t="n">
         <v>104</v>
@@ -2039,7 +2103,7 @@
         <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -2048,56 +2112,61 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.391</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>0.997</v>
+        <v>0.4137599894534391</v>
       </c>
       <c r="N27" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="O27" t="inlineStr">
+        <v>0.476487079765587</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.4749469200156592</v>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-90989-111207597</t>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-90989-111207233</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>idealista_110486816</t>
+          <t>yaencontre_inmueble-86283-Promo-1-109242399</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chalet pareado en Calle d'Anselm Clavé, Martinica-Ateneu, Cerdanyola del Vallès</t>
+          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>580000</v>
+        <v>533000</v>
       </c>
       <c r="E28" t="n">
-        <v>282</v>
+        <v>119</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
       <c r="H28" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -2106,32 +2175,35 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.799</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.435</v>
       </c>
       <c r="M28" t="n">
-        <v>0.006</v>
+        <v>0.5041425796408956</v>
       </c>
       <c r="N28" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="O28" t="inlineStr">
+        <v>0.457144134410051</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.4720561660910605</v>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/110486816/</t>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-109242399</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>idealista_110486766</t>
+          <t>idealista_111207597</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2141,21 +2213,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chalet pareado en Calle d'Anselm Clavé, Martinica-Ateneu, Cerdanyola del Vallès</t>
+          <t>Piso en Rambla de Montserrat, 9, Fontetes, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>580000</v>
+        <v>500000</v>
       </c>
       <c r="E29" t="n">
-        <v>282</v>
+        <v>104</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
       <c r="H29" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -2164,32 +2238,35 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0.799</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="M29" t="n">
-        <v>0.006</v>
+        <v>0.4104339009430577</v>
       </c>
       <c r="N29" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="O29" t="inlineStr">
+        <v>0.352518006664424</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.4714546018761245</v>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/110486766/</t>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111207597/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>idealista_110757335</t>
+          <t>idealista_111718387</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2199,21 +2276,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chalet adosado en Calle de Sant Ramon, Sant Ramón, Cerdanyola del Vallès</t>
+          <t>Piso en Calle de Creu Casas i Sicart, 1, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>595000</v>
+        <v>494000</v>
       </c>
       <c r="E30" t="n">
-        <v>343</v>
+        <v>120</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0.02</v>
+        <v>33.23883179740741</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -2222,58 +2299,59 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.766</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="M30" t="n">
-        <v>0.006</v>
+        <v>0.4296700442264185</v>
       </c>
       <c r="N30" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="O30" t="inlineStr">
+        <v>0.3188707977015703</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.4645867007107081</v>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/110757335/</t>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111718387/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-86283-Promo-1-109242405</t>
+          <t>idealista_110755540</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>586000</v>
+        <v>487000</v>
       </c>
       <c r="E31" t="n">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
-      </c>
-      <c r="G31" t="n">
         <v>3</v>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -2282,58 +2360,59 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.786</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.555</v>
+        <v>0.5349999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>0.013</v>
+        <v>0.4362904005022795</v>
       </c>
       <c r="N31" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="O31" t="inlineStr">
+        <v>0.3543000250486575</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.4611316344486328</v>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-109242405</t>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110755540/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-86283-Promo-1-109242406</t>
+          <t>idealista_111333235</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en Còrdova s/n, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>570000</v>
+        <v>533000</v>
       </c>
       <c r="E32" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -2342,58 +2421,59 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.517</v>
+        <v>0.435</v>
       </c>
       <c r="M32" t="n">
-        <v>0.018</v>
+        <v>0.5145491312234711</v>
       </c>
       <c r="N32" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="O32" t="inlineStr">
+        <v>0.3543013860179364</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.4610005054969251</v>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-109242406</t>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111333235/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-86283-Promo-1-110755540</t>
+          <t>idealista_111718398</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en Calle de Creu Casas i Sicart, 1, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>487000</v>
+        <v>530000</v>
       </c>
       <c r="E33" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
-      </c>
-      <c r="G33" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0.02</v>
+        <v>33.23883179740741</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -2402,58 +2482,59 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.368</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.432</v>
+        <v>0.45</v>
       </c>
       <c r="M33" t="n">
-        <v>0.997</v>
+        <v>0.5138679766757783</v>
       </c>
       <c r="N33" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="O33" t="inlineStr">
+        <v>0.3179082484571978</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.4602054499527833</v>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-110755540</t>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111718398/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-59941-110271317</t>
+          <t>idealista_111333124</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ático en Sant Ramon, Cerdanyola del Vallès</t>
+          <t>Piso en Còrdova s/n, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>677500</v>
+        <v>527000</v>
       </c>
       <c r="E34" t="n">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="F34" t="n">
         <v>4</v>
       </c>
-      <c r="G34" t="n">
-        <v>2</v>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -2462,42 +2543,45 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.173</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.573</v>
+        <v>0.465</v>
       </c>
       <c r="M34" t="n">
-        <v>0.997</v>
+        <v>0.4854764597369234</v>
       </c>
       <c r="N34" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.3539081731813232</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.458631001547083</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-59941-110271317</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111333124/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-90989-111207233</t>
+          <t>idealista_111207233</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Piso en rambla De Montserrat en Catalunya - Fontetes, Cerdanyola del Vallès</t>
+          <t>Piso en Rambla de Montserrat, 9, Fontetes, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2513,7 +2597,7 @@
         <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -2522,58 +2606,59 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.391</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.394</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>0.998</v>
+        <v>0.4137599894534391</v>
       </c>
       <c r="N35" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="O35" t="inlineStr">
+        <v>0.350373569596086</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.456029893490234</v>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-90989-111207233</t>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111207233/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-53321-Promo-77-111179871</t>
+          <t>idealista_111333224</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en Còrdova s/n, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>468000</v>
+        <v>514000</v>
       </c>
       <c r="E36" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F36" t="n">
         <v>3</v>
       </c>
-      <c r="G36" t="n">
-        <v>2</v>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
@@ -2582,56 +2667,61 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0.219</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.519</v>
+        <v>0.5299999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>0.999</v>
+        <v>0.4273886397720437</v>
       </c>
       <c r="N36" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="O36" t="inlineStr">
+        <v>0.3547887423176717</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.4558162025322858</v>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-77-111179871</t>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111333224/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>idealista_109242405</t>
+          <t>yaencontre_inmueble-58132-Promo-33-111333196</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Piso en calle Còrdova en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>586000</v>
+        <v>450000</v>
       </c>
       <c r="E37" t="n">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
       <c r="H37" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -2640,32 +2730,35 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.786</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.517</v>
+        <v>0.3499999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>0.007</v>
+        <v>0.5267482009528528</v>
       </c>
       <c r="N37" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="O37" t="inlineStr">
+        <v>0.4507943636688186</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.4525480614308978</v>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/109242405/</t>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-58132-Promo-33-111333196</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>idealista_111623649</t>
+          <t>idealista_111628567</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2675,21 +2768,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chalet adosado en Rambla de Montserrat, Fontetes, Cerdanyola del Vallès</t>
+          <t>Chalet adosado en Montflorit-Plana del Castell, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>580000</v>
+        <v>545000</v>
       </c>
       <c r="E38" t="n">
-        <v>343</v>
+        <v>214</v>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -2698,32 +2791,35 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.799</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.498</v>
+        <v>0.375</v>
       </c>
       <c r="M38" t="n">
-        <v>0.005</v>
+        <v>0.5350608310389531</v>
       </c>
       <c r="N38" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="O38" t="inlineStr">
+        <v>0.354273979617455</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.4498113084593552</v>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>within target band, strong size</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/111623649/</t>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111628567/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>idealista_108228205</t>
+          <t>idealista_111003072</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2733,21 +2829,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chalet adosado en Ronda Serraparera, Serraparera, Cerdanyola del Vallès</t>
+          <t>Chalet adosado en Calle Marqués de Comillas, 125, Zona Esportiva, Terrassa</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>615000</v>
-      </c>
-      <c r="E39" t="n">
-        <v>196</v>
-      </c>
-      <c r="F39" t="n">
-        <v>4</v>
-      </c>
+        <v>494000</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -2756,56 +2848,61 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.626</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.622</v>
+        <v>0.57</v>
       </c>
       <c r="M39" t="n">
-        <v>0.008</v>
+        <v>0.3803079680948892</v>
       </c>
       <c r="N39" t="n">
-        <v>0.501</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.3536694200545519</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.449074422088413</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/108228205/</t>
+          <t>within target band</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111003072/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>idealista_111628567</t>
+          <t>yaencontre_inmueble-52952-108234940</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Casa o chalet en Montflorit-Plana del Castell, Cerdanyola del Vallès</t>
+          <t>Dúplex en calle De la Serra de Galliners en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>545000</v>
+        <v>480000</v>
       </c>
       <c r="E40" t="n">
-        <v>214</v>
+        <v>93</v>
       </c>
       <c r="F40" t="n">
         <v>3</v>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
       <c r="H40" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
@@ -2814,58 +2911,59 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0.824</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.469</v>
+        <v>0.5</v>
       </c>
       <c r="M40" t="n">
-        <v>0.005</v>
+        <v>0.3914537002235171</v>
       </c>
       <c r="N40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>within target band, strong size</t>
-        </is>
+        <v>0.4724605812161869</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.448474303756682</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111628567/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-52952-108234940</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-90989-111207022</t>
+          <t>idealista_111970380</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Piso en rambla De Montserrat en Catalunya - Fontetes, Cerdanyola del Vallès</t>
+          <t>Casa o chalet en Calle de Bèlgica, Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>650000</v>
+        <v>527000</v>
       </c>
       <c r="E41" t="n">
-        <v>105</v>
+        <v>245</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>0.02</v>
+        <v>5.040452167777778</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
@@ -2874,32 +2972,35 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.351</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.384</v>
+        <v>0.465</v>
       </c>
       <c r="M41" t="n">
-        <v>0.996</v>
+        <v>0.561724661135055</v>
       </c>
       <c r="N41" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.05026097915622461</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.4451081670305336</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-90989-111207022</t>
+          <t>within target band, strong size</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111970380/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>idealista_110659374</t>
+          <t>idealista_110755511</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2909,21 +3010,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Piso en Calle de la Ciència, 5, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>600000</v>
+        <v>521000</v>
       </c>
       <c r="E42" t="n">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
@@ -2932,32 +3033,35 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.744</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.516</v>
+        <v>0.4949999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>0.006</v>
+        <v>0.4279502679776131</v>
       </c>
       <c r="N42" t="n">
-        <v>0.494</v>
-      </c>
-      <c r="O42" t="inlineStr">
+        <v>0.3538465926066756</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.4443607639219755</v>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/110659374/</t>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110755511/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>idealista_111333235</t>
+          <t>idealista_110586775</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2967,21 +3071,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Piso en Còrdova s/n, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Piso en CL Josep Tarradellas, Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>533000</v>
+        <v>529000</v>
       </c>
       <c r="E43" t="n">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="F43" t="n">
         <v>4</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
@@ -2990,32 +3094,35 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.729</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.498</v>
+        <v>0.455</v>
       </c>
       <c r="M43" t="n">
-        <v>0.006</v>
+        <v>0.4487484106239069</v>
       </c>
       <c r="N43" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="O43" t="inlineStr">
+        <v>0.351363311590969</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.439523491681063</v>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/111333235/</t>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110586775/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>idealista_111526446</t>
+          <t>idealista_110627382</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3025,7 +3132,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Piso en Calle de Josep Tarradellas, Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en CL Josep Tarradellas, Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -3039,7 +3146,7 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
@@ -3048,58 +3155,59 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0.698</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.519</v>
+        <v>0.455</v>
       </c>
       <c r="M44" t="n">
-        <v>0.008</v>
+        <v>0.4487484106239069</v>
       </c>
       <c r="N44" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="O44" t="inlineStr">
+        <v>0.351363311590969</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.439523491681063</v>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/111526446/</t>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110627382/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-86283-Promo-1-109242399</t>
+          <t>idealista_112000276</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
+          <t>Casa o chalet independiente en Passatge de Maria Lluïsa, Sant Ramón, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>533000</v>
+        <v>498000</v>
       </c>
       <c r="E45" t="n">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="F45" t="n">
         <v>3</v>
       </c>
-      <c r="G45" t="n">
-        <v>2</v>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>0.02</v>
+        <v>1.970510038148148</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
@@ -3108,32 +3216,35 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0.729</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.487</v>
+        <v>0.59</v>
       </c>
       <c r="M45" t="n">
-        <v>0.017</v>
+        <v>0.4581871233891252</v>
       </c>
       <c r="N45" t="n">
-        <v>0.478</v>
-      </c>
-      <c r="O45" t="inlineStr">
+        <v>0.02281238278107183</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.4387551117209701</v>
+      </c>
+      <c r="P45" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-109242399</t>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/112000276/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>idealista_111501478</t>
+          <t>idealista_111087576</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3143,79 +3254,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Piso en Calle de Creu Casas i Sicart, 1, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Casa o chalet independiente en Caneletes-Turonet, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>530000</v>
+        <v>599000</v>
       </c>
       <c r="E46" t="n">
-        <v>138</v>
+        <v>230</v>
       </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0.706</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.497</v>
+        <v>0.105</v>
       </c>
       <c r="M46" t="n">
-        <v>0.007</v>
+        <v>0.5661093850596488</v>
       </c>
       <c r="N46" t="n">
-        <v>0.472</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.7867669035374568</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.4386256397360477</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111501478/</t>
+          <t>within target band, 1 price cut(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111087576/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>idealista_109242406</t>
+          <t>yaencontre_inmueble-90989-111207273</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Piso en rambla De Montserrat en Catalunya - Fontetes, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>570000</v>
+        <v>470000</v>
       </c>
       <c r="E47" t="n">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="F47" t="n">
         <v>3</v>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
       <c r="H47" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
@@ -3224,58 +3340,59 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.403</v>
+        <v>0.45</v>
       </c>
       <c r="M47" t="n">
-        <v>0.005</v>
+        <v>0.4009634436720704</v>
       </c>
       <c r="N47" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.470447363246002</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.4356664133095466</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/109242406/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-90989-111207273</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-58132-Promo-33-111333196</t>
+          <t>idealista_109242345</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Piso en calle Còrdova en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>450000</v>
+        <v>485000</v>
       </c>
       <c r="E48" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F48" t="n">
         <v>3</v>
       </c>
-      <c r="G48" t="n">
-        <v>2</v>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>0.02</v>
+        <v>18.17630864925926</v>
       </c>
       <c r="I48" t="n">
         <v>1</v>
@@ -3284,32 +3401,35 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.506</v>
+        <v>0.525</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0.4440138406371867</v>
       </c>
       <c r="N48" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="O48" t="inlineStr">
+        <v>0.1736129994632696</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.4339724254674856</v>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-58132-Promo-33-111333196</t>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/109242345/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>idealista_108314161</t>
+          <t>idealista_111718386</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3319,21 +3439,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Casa o chalet en Ronda Serraparera, Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en Calle de Creu Casas i Sicart, 1, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>615000</v>
+        <v>468000</v>
       </c>
       <c r="E49" t="n">
-        <v>196</v>
+        <v>120</v>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>0.02</v>
+        <v>33.23883179740741</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
@@ -3342,32 +3462,35 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0.626</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.535</v>
+        <v>0.44</v>
       </c>
       <c r="M49" t="n">
-        <v>0.006</v>
+        <v>0.4476840538255883</v>
       </c>
       <c r="N49" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.313927751650616</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.4285111278347162</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/108314161/</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111718386/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>idealista_111087576</t>
+          <t>idealista_108234940</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3377,21 +3500,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Casa o chalet independiente en Calle de Pizarro, Caneletes-Turonet, Cerdanyola del Vallès</t>
+          <t>Dúplex en Calle de la Serra de Galliners, 12, Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>620000</v>
+        <v>480000</v>
       </c>
       <c r="E50" t="n">
-        <v>230</v>
+        <v>93</v>
       </c>
       <c r="F50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I50" t="n">
         <v>1</v>
@@ -3400,32 +3523,35 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0.587</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M50" t="n">
-        <v>0.006</v>
+        <v>0.3866656311497337</v>
       </c>
       <c r="N50" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>near target band, strong size</t>
-        </is>
+        <v>0.3477691420812063</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.4277595988754459</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111087576/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/108234940/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>idealista_111554232</t>
+          <t>idealista_111915704</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3435,21 +3561,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Casa o chalet independiente en Caneletes-Turonet, Cerdanyola del Vallès</t>
+          <t>Piso en Calle de la Ciència, 5, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>620000</v>
+        <v>509000</v>
       </c>
       <c r="E51" t="n">
-        <v>230</v>
+        <v>123</v>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>0.02</v>
+        <v>11.0395956862963</v>
       </c>
       <c r="I51" t="n">
         <v>1</v>
@@ -3458,52 +3584,61 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0.587</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.555</v>
       </c>
       <c r="M51" t="n">
-        <v>0.006</v>
+        <v>0.425690995089576</v>
       </c>
       <c r="N51" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>near target band, strong size</t>
-        </is>
+        <v>0.1062664935694352</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.426074854453414</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111554232/</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111915704/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>idealista_111315640</t>
+          <t>yaencontre_inmueble-53321-Promo-75-110659374</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Piso en Calle independencia, 288, El Camp de l'Arpa del Clot, Barcelona</t>
+          <t>Piso en calle De la Ciència en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>550000</v>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+        <v>600000</v>
+      </c>
+      <c r="E52" t="n">
+        <v>161</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3</v>
+      </c>
       <c r="H52" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I52" t="n">
         <v>1</v>
@@ -3512,56 +3647,61 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0.863</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0.348</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="M52" t="n">
-        <v>0.004</v>
+        <v>0.6555849366347846</v>
       </c>
       <c r="N52" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>within target band</t>
-        </is>
+        <v>0.4624195146014574</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.4259032630572048</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111315640/</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-75-110659374</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>idealista_111142454</t>
+          <t>yaencontre_inmueble-86283-Promo-1-111969683</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Piso en Calle de la Ciència, 5, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>613000</v>
+        <v>540000</v>
       </c>
       <c r="E53" t="n">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2</v>
+      </c>
       <c r="H53" t="n">
-        <v>0.02</v>
+        <v>5.040452167777778</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
@@ -3570,56 +3710,61 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0.642</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0.516</v>
+        <v>0.4</v>
       </c>
       <c r="M53" t="n">
-        <v>0.006</v>
+        <v>0.530112225509361</v>
       </c>
       <c r="N53" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.151223687451468</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.4255253503120285</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111142454/</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-111969683</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>idealista_111333234</t>
+          <t>yaencontre_inmueble-86283-Promo-1-109242406</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Piso en Còrdova s/n, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>524000</v>
+        <v>570000</v>
       </c>
       <c r="E54" t="n">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2</v>
+      </c>
       <c r="H54" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -3628,32 +3773,35 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0.659</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0.496</v>
+        <v>0.25</v>
       </c>
       <c r="M54" t="n">
-        <v>0.006</v>
+        <v>0.5325664467879621</v>
       </c>
       <c r="N54" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="O54" t="inlineStr">
+        <v>0.4520442473572193</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.4221792072349037</v>
+      </c>
+      <c r="P54" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/111333234/</t>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-109242406</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>idealista_110632840</t>
+          <t>idealista_111207273</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3663,21 +3811,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Piso en Calle de Josep Tarradellas, Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en Rambla de Montserrat, 9, Fontetes, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>529000</v>
+        <v>470000</v>
       </c>
       <c r="E55" t="n">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
-      </c>
-      <c r="G55" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2</v>
+      </c>
       <c r="H55" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
@@ -3686,32 +3836,35 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0.698</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0.463</v>
+        <v>0.45</v>
       </c>
       <c r="M55" t="n">
-        <v>0.006</v>
+        <v>0.4009634436720704</v>
       </c>
       <c r="N55" t="n">
-        <v>0.454</v>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.344333853076501</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.4167493867841214</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110632840/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111207273/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-90989-111207273</t>
+          <t>yaencontre_inmueble-86283-Promo-1-109242405</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3721,23 +3874,23 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Piso en rambla De Montserrat en Catalunya - Fontetes, Cerdanyola del Vallès</t>
+          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>470000</v>
+        <v>586000</v>
       </c>
       <c r="E56" t="n">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="F56" t="n">
+        <v>4</v>
+      </c>
+      <c r="G56" t="n">
         <v>3</v>
       </c>
-      <c r="G56" t="n">
-        <v>2</v>
-      </c>
       <c r="H56" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
@@ -3746,32 +3899,35 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0.234</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0.38</v>
+        <v>0.17</v>
       </c>
       <c r="M56" t="n">
-        <v>0.998</v>
+        <v>0.5686709400074659</v>
       </c>
       <c r="N56" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>within target band, good profile match</t>
-        </is>
+        <v>0.4838269657904603</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.4157105021520815</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-90989-111207273</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-109242405</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>idealista_111058444</t>
+          <t>idealista_110870946</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3781,17 +3937,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Piso en Calle Arenys y Pluto, 109, La Teixonera, Barcelona</t>
+          <t>Piso en Calle Torre D´en Damians, 16, Hostafrancs, Barcelona</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>560000</v>
+        <v>464500</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
@@ -3800,32 +3956,35 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0.841</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0.348</v>
+        <v>0.4224999999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>0.004</v>
+        <v>0.4113911706066631</v>
       </c>
       <c r="N57" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>within target band</t>
-        </is>
+        <v>0.3485831722096795</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.4126914299666272</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111058444/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110870946/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>idealista_111333124</t>
+          <t>idealista_109242399</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3835,21 +3994,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Piso en Còrdova s/n, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>527000</v>
+        <v>533000</v>
       </c>
       <c r="E58" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I58" t="n">
         <v>1</v>
@@ -3858,56 +4017,61 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0.6820000000000001</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0.468</v>
+        <v>0.435</v>
       </c>
       <c r="M58" t="n">
-        <v>0.006</v>
+        <v>0.3995742907868925</v>
       </c>
       <c r="N58" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="O58" t="inlineStr">
+        <v>0.3498460361909971</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.4120427700395212</v>
+      </c>
+      <c r="P58" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/111333124/</t>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/109242399/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>idealista_111411842</t>
+          <t>yaencontre_inmueble-91376-Promo-8-111284757</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Piso en Calle de la Ciència, 5, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Piso en calle Del Pont en Catalunya - Fontetes, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>616000</v>
+        <v>534000</v>
       </c>
       <c r="E59" t="n">
-        <v>170</v>
+        <v>87</v>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
-      </c>
-      <c r="G59" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2</v>
+      </c>
       <c r="H59" t="n">
-        <v>0.02</v>
+        <v>12.03951466777778</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
@@ -3916,58 +4080,59 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0.619</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0.515</v>
+        <v>0.43</v>
       </c>
       <c r="M59" t="n">
-        <v>0.006</v>
+        <v>0.4419087739380463</v>
       </c>
       <c r="N59" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.2122850365976085</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.4075391030239975</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111411842/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-91376-Promo-8-111284757</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-91376-Promo-8-111071062</t>
+          <t>idealista_110486816</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Piso en calle Del Pont en Catalunya - Fontetes, Cerdanyola del Vallès</t>
+          <t>Chalet pareado en Calle d'Anselm Clavé, Martinica-Ateneu, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>460000</v>
+        <v>580000</v>
       </c>
       <c r="E60" t="n">
-        <v>85</v>
+        <v>282</v>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
-      </c>
-      <c r="G60" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
@@ -3976,32 +4141,35 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0.156</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0.434</v>
+        <v>0.2</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>0.5723217055535014</v>
       </c>
       <c r="N60" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>within target band, good profile match</t>
-        </is>
+        <v>0.3490867846014836</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.4069327965030699</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-91376-Promo-8-111071062</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110486816/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>idealista_110324575</t>
+          <t>idealista_110486766</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4011,21 +4179,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ático en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Chalet pareado en Calle d'Anselm Clavé, Martinica-Ateneu, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>589000</v>
+        <v>580000</v>
       </c>
       <c r="E61" t="n">
-        <v>122</v>
+        <v>282</v>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
@@ -4034,32 +4202,35 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0.779</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0.384</v>
+        <v>0.2</v>
       </c>
       <c r="M61" t="n">
-        <v>0.005</v>
+        <v>0.5723217055535014</v>
       </c>
       <c r="N61" t="n">
-        <v>0.446</v>
-      </c>
-      <c r="O61" t="inlineStr">
+        <v>0.3490867846014836</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.4069327965030699</v>
+      </c>
+      <c r="P61" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/110324575/</t>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110486766/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>idealista_111457642</t>
+          <t>idealista_111358939</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4069,79 +4240,84 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Casa o chalet independiente en Avenida de la Flor de Maig, Sant Ramón, Cerdanyola del Vallès</t>
+          <t>Casa o chalet independiente en Calle Sentmenat, 30, Montflorit-Plana del Castell, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>517000</v>
+        <v>689000</v>
       </c>
       <c r="E62" t="n">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>0.604</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.005</v>
+        <v>0.5644402519763988</v>
       </c>
       <c r="N62" t="n">
-        <v>0.446</v>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>within target band, strong size</t>
-        </is>
+        <v>0.7974528742271878</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.4048774994445424</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111457642/</t>
+          <t>near target band, 1 price cut(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111358939/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>idealista_110627382</t>
+          <t>yaencontre_inmueble-53321-Promo-75-111142454</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Piso en CL Josep Tarradellas, Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en calle De la Ciència en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>529000</v>
+        <v>613000</v>
       </c>
       <c r="E63" t="n">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="F63" t="n">
         <v>4</v>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>3</v>
+      </c>
       <c r="H63" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -4150,32 +4326,35 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0.698</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0.429</v>
+        <v>0.03500000000000001</v>
       </c>
       <c r="M63" t="n">
-        <v>0.006</v>
+        <v>0.6557872975116817</v>
       </c>
       <c r="N63" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.4600546213961328</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.404183520644703</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110627382/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-75-111142454</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>idealista_110586775</t>
+          <t>idealista_111333196</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4185,21 +4364,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Piso en CL Josep Tarradellas, Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en Còrdova s/n, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>529000</v>
+        <v>450000</v>
       </c>
       <c r="E64" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I64" t="n">
         <v>1</v>
@@ -4208,56 +4387,61 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0.698</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0.429</v>
+        <v>0.3499999999999999</v>
       </c>
       <c r="M64" t="n">
-        <v>0.006</v>
+        <v>0.4440794411412358</v>
       </c>
       <c r="N64" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="O64" t="inlineStr">
+        <v>0.3452579612195693</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.4019967219426311</v>
+      </c>
+      <c r="P64" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/110586775/</t>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111333196/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>idealista_111521058</t>
+          <t>yaencontre_inmueble-53321-Promo-75-111411842</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dúplex en Calle de la Mare de Déu de les Feixes, Caneletes-Turonet, Cerdanyola del Vallès</t>
+          <t>Piso en calle De la Ciència en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>515000</v>
+        <v>616000</v>
       </c>
       <c r="E65" t="n">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="F65" t="n">
         <v>4</v>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="n">
+        <v>3</v>
+      </c>
       <c r="H65" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
@@ -4266,32 +4450,35 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0.588</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0.499</v>
+        <v>0.01999999999999999</v>
       </c>
       <c r="M65" t="n">
-        <v>0.006</v>
+        <v>0.6572751953040846</v>
       </c>
       <c r="N65" t="n">
-        <v>0.432</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.4598367207257624</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.3998257526169566</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111521058/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-53321-Promo-75-111411842</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>idealista_110833654</t>
+          <t>idealista_109664462</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4301,21 +4488,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chalet pareado en Avenida de Canaletes, Caneletes-Turonet, Cerdanyola del Vallès</t>
+          <t>Piso en Carretera Reial, 128, Mas Lluí - Els Miralls, Sant Just Desvern</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>625000</v>
-      </c>
-      <c r="E66" t="n">
-        <v>170</v>
-      </c>
-      <c r="F66" t="n">
-        <v>5</v>
-      </c>
+        <v>454000</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
@@ -4324,90 +4507,98 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0.548</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0.529</v>
+        <v>0.37</v>
       </c>
       <c r="M66" t="n">
-        <v>0.006</v>
+        <v>0.4204963511404151</v>
       </c>
       <c r="N66" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.3466458957219637</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.3989000143176457</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110833654/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/109664462/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>idealista_109242399</t>
+          <t>yaencontre_inmueble-90989-111207361</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Ático en rambla De Montserrat en Catalunya - Fontetes, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>533000</v>
+        <v>450000</v>
       </c>
       <c r="E67" t="n">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
-      </c>
-      <c r="G67" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2</v>
+      </c>
       <c r="H67" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.729</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0.38</v>
+        <v>0.3499999999999999</v>
       </c>
       <c r="M67" t="n">
-        <v>0.006</v>
+        <v>0.3048792228840965</v>
       </c>
       <c r="N67" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.6798230120432999</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.3937173878981922</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/109242399/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-90989-111207361</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>idealista_111637945</t>
+          <t>idealista_110757335</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4417,21 +4608,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chalet adosado en Calle de les Vinyes, 3, Martinica-Ateneu, Cerdanyola del Vallès</t>
+          <t>Chalet adosado en Calle de Sant Ramon, Sant Ramón, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>635000</v>
+        <v>595000</v>
       </c>
       <c r="E68" t="n">
-        <v>202</v>
+        <v>343</v>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I68" t="n">
         <v>1</v>
@@ -4440,32 +4631,35 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.469</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0.542</v>
+        <v>0.125</v>
       </c>
       <c r="M68" t="n">
-        <v>0.006</v>
+        <v>0.5901644867183737</v>
       </c>
       <c r="N68" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>near target band, strong size</t>
-        </is>
+        <v>0.3464905282040073</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.3892873261326948</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111637945/</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110757335/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>idealista_111385063</t>
+          <t>idealista_109992648</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4475,21 +4669,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Piso en Calle de la Ciència, 5, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Piso en de Lloreda, 132, Montigalà, Badalona</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>525000</v>
-      </c>
-      <c r="E69" t="n">
-        <v>119</v>
-      </c>
-      <c r="F69" t="n">
-        <v>3</v>
-      </c>
+        <v>455000</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>0.02</v>
+        <v>26.05813735296297</v>
       </c>
       <c r="I69" t="n">
         <v>1</v>
@@ -4498,56 +4688,61 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0.666</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0.386</v>
+        <v>0.375</v>
       </c>
       <c r="M69" t="n">
-        <v>0.006</v>
+        <v>0.4164932114229897</v>
       </c>
       <c r="N69" t="n">
-        <v>0.408</v>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.2412770730489943</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.3830633722353816</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111385063/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/109992648/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>idealista_110755511</t>
+          <t>yaencontre_inmueble-86283-Promo-1-110324575</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Piso en calle De Creu Casas i Sicart en Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>521000</v>
+        <v>589000</v>
       </c>
       <c r="E70" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F70" t="n">
         <v>3</v>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="n">
+        <v>2</v>
+      </c>
       <c r="H70" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
@@ -4556,32 +4751,35 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0.635</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>0.409</v>
+        <v>0.155</v>
       </c>
       <c r="M70" t="n">
-        <v>0.006</v>
+        <v>0.5144551483056685</v>
       </c>
       <c r="N70" t="n">
-        <v>0.408</v>
-      </c>
-      <c r="O70" t="inlineStr">
+        <v>0.4472797468103603</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.3825077867903116</v>
+      </c>
+      <c r="P70" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/110755511/</t>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-86283-Promo-1-110324575</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>idealista_110692215</t>
+          <t>idealista_111623649</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4591,21 +4789,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Piso en Serraparera, Cerdanyola del Vallès</t>
+          <t>Chalet adosado en Rambla de Montserrat, Fontetes, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>515000</v>
+        <v>580000</v>
       </c>
       <c r="E71" t="n">
-        <v>116</v>
+        <v>343</v>
       </c>
       <c r="F71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I71" t="n">
         <v>1</v>
@@ -4614,32 +4812,35 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0.588</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0.412</v>
+        <v>0.2</v>
       </c>
       <c r="M71" t="n">
-        <v>0.006</v>
+        <v>0.509395782232089</v>
       </c>
       <c r="N71" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="O71" t="inlineStr">
+        <v>0.347058668802523</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.3801996913382326</v>
+      </c>
+      <c r="P71" t="inlineStr">
         <is>
           <t>within target band, strong size</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/110692215/</t>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111623649/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>idealista_111333224</t>
+          <t>idealista_109242405</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4649,21 +4850,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Piso en Còrdova s/n, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>514000</v>
+        <v>586000</v>
       </c>
       <c r="E72" t="n">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I72" t="n">
         <v>1</v>
@@ -4672,32 +4873,35 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0.408</v>
+        <v>0.17</v>
       </c>
       <c r="M72" t="n">
-        <v>0.006</v>
+        <v>0.532811565007466</v>
       </c>
       <c r="N72" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="O72" t="inlineStr">
+        <v>0.3452468439263188</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.3798625463724602</v>
+      </c>
+      <c r="P72" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/111333224/</t>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/109242405/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>idealista_110755547</t>
+          <t>idealista_111284757</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4707,21 +4911,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Piso en Paseo del Pont, 31, Fontetes, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>516000</v>
+        <v>534000</v>
       </c>
       <c r="E73" t="n">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="F73" t="n">
         <v>3</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>0.02</v>
+        <v>12.03951466777778</v>
       </c>
       <c r="I73" t="n">
         <v>1</v>
@@ -4730,32 +4934,35 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.596</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0.396</v>
+        <v>0.43</v>
       </c>
       <c r="M73" t="n">
-        <v>0.006</v>
+        <v>0.4182824003116727</v>
       </c>
       <c r="N73" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.08577687192511094</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.3786398014000459</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110755547/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111284757/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>idealista_110719246</t>
+          <t>idealista_111826265</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4765,21 +4972,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chalet adosado en Av Flor De Maig, Sant Ramón, Cerdanyola del Vallès</t>
+          <t>Piso en Plaza Eivissa, 1, Horta, Barcelona</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>650000</v>
-      </c>
-      <c r="E74" t="n">
-        <v>217</v>
-      </c>
-      <c r="F74" t="n">
-        <v>5</v>
-      </c>
+        <v>530098</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>0.02</v>
+        <v>18.17630864925926</v>
       </c>
       <c r="I74" t="n">
         <v>1</v>
@@ -4788,32 +4991,35 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.351</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.44951</v>
       </c>
       <c r="M74" t="n">
-        <v>0.006</v>
+        <v>0.3647663668390022</v>
       </c>
       <c r="N74" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.1684945907793083</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.375009025169654</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110719246/</t>
+          <t>within target band</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111826265/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>idealista_110936543</t>
+          <t>idealista_111207361</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4823,55 +5029,60 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chalet adosado en Calle de la Sínia, Fontetes, Cerdanyola del Vallès</t>
+          <t>Ático en Rambla de Montserrat, 9, Fontetes, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>490000</v>
+        <v>450000</v>
       </c>
       <c r="E75" t="n">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="F75" t="n">
-        <v>4</v>
-      </c>
-      <c r="G75" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
       <c r="H75" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.391</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0.526</v>
+        <v>0.3499999999999999</v>
       </c>
       <c r="M75" t="n">
-        <v>0.006</v>
+        <v>0.3036233359139239</v>
       </c>
       <c r="N75" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>within target band, strong size</t>
-        </is>
+        <v>0.553759062880507</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.3742803229963009</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110936543/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111207361/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>idealista_111202237</t>
+          <t>idealista_111992300</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4881,21 +5092,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ático en Avenida de Lesseps, Caneletes-Turonet, Cerdanyola del Vallès</t>
+          <t>Chalet adosado en Montflorit-Plana del Castell, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>476000</v>
+        <v>530000</v>
       </c>
       <c r="E76" t="n">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="F76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>0.02</v>
+        <v>3.197026241851852</v>
       </c>
       <c r="I76" t="n">
         <v>1</v>
@@ -4904,32 +5115,35 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.281</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="M76" t="n">
-        <v>0.008</v>
+        <v>0.4077252460710687</v>
       </c>
       <c r="N76" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="O76" t="inlineStr">
+        <v>0.0269912421987332</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.3719879521600356</v>
+      </c>
+      <c r="P76" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/111202237/</t>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111992300/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>idealista_110575720</t>
+          <t>idealista_108228205</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4939,21 +5153,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chalet adosado en Rd Cerdanyola, Caneletes-Turonet, Cerdanyola del Vallès</t>
+          <t>Chalet adosado en Ronda Serraparera, Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>650000</v>
+        <v>615000</v>
       </c>
       <c r="E77" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F77" t="n">
         <v>4</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -4962,32 +5176,35 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.351</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0.541</v>
+        <v>0.02499999999999998</v>
       </c>
       <c r="M77" t="n">
-        <v>0.007</v>
+        <v>0.6349809614987125</v>
       </c>
       <c r="N77" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="O77" t="inlineStr">
+        <v>0.3223893791121146</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.3714950731766532</v>
+      </c>
+      <c r="P77" t="inlineStr">
         <is>
           <t>near target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/110575720/</t>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/108228205/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>idealista_108639634</t>
+          <t>idealista_111315640</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4997,21 +5214,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Casa o chalet en Calle de Pizarro, Caneletes-Turonet, Cerdanyola del Vallès</t>
+          <t>Piso en Calle independencia, 288, El Camp de l'Arpa del Clot, Barcelona</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>660000</v>
-      </c>
-      <c r="E78" t="n">
-        <v>291</v>
-      </c>
-      <c r="F78" t="n">
-        <v>7</v>
-      </c>
+        <v>550000</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I78" t="n">
         <v>1</v>
@@ -5020,32 +5233,35 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0.601</v>
+        <v>0.3499999999999999</v>
       </c>
       <c r="M78" t="n">
-        <v>0.006</v>
+        <v>0.3552687216270713</v>
       </c>
       <c r="N78" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.3453183559535103</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.3647052789567733</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/108639634/</t>
+          <t>within target band</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111315640/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>idealista_111206916</t>
+          <t>idealista_111058407</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5055,23 +5271,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Piso en Rambla de Montserrat, 9, Fontetes, Cerdanyola del Vallès</t>
+          <t>Dúplex en Calle Arenys y Pluto, 109, La Teixonera, Barcelona</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>625000</v>
-      </c>
-      <c r="E79" t="n">
-        <v>105</v>
-      </c>
-      <c r="F79" t="n">
-        <v>3</v>
-      </c>
-      <c r="G79" t="n">
-        <v>2</v>
-      </c>
+        <v>464000</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>0.02</v>
+        <v>4.076910501111112</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
@@ -5080,56 +5290,61 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.548</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0.384</v>
+        <v>0.42</v>
       </c>
       <c r="M79" t="n">
-        <v>0.007</v>
+        <v>0.4113911706066631</v>
       </c>
       <c r="N79" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.03266629703459571</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.3644788986903646</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111206916/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111058407/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>idealista_110755512</t>
+          <t>yaencontre_inmueble-59941-110271317</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Ático en Sant Ramon, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>503000</v>
+        <v>677500</v>
       </c>
       <c r="E80" t="n">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
-      </c>
-      <c r="G80" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2</v>
+      </c>
       <c r="H80" t="n">
-        <v>0.02</v>
+        <v>37.07041744555556</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -5138,32 +5353,35 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.494</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>0.006</v>
+        <v>0.5846282859882438</v>
       </c>
       <c r="N80" t="n">
-        <v>0.362</v>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.4683603739884541</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.3639925986937073</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110755512/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-59941-110271317</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>idealista_111105534</t>
+          <t>idealista_111747224</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5173,21 +5391,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dúplex en Calle de Pompeu Fabra, 17, Caneletes-Turonet, Cerdanyola del Vallès</t>
+          <t>Chalet adosado en Avenida de la Flor de Maig, Sant Ramón, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>490000</v>
+        <v>650000</v>
       </c>
       <c r="E81" t="n">
-        <v>107</v>
+        <v>217</v>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>0.02</v>
+        <v>29.11203781592593</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
@@ -5196,32 +5414,35 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.391</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0.482</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.6622138852330481</v>
       </c>
       <c r="N81" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.2450594468692237</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.3630834113086405</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111105534/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111747224/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>idealista_111357087</t>
+          <t>idealista_111969683</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5231,21 +5452,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dúplex en Calle de Sant Ramon, 197, Sant Ramón, Cerdanyola del Vallès</t>
+          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>473000</v>
+        <v>540000</v>
       </c>
       <c r="E82" t="n">
-        <v>190</v>
+        <v>129</v>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>0.02</v>
+        <v>5.040452167777778</v>
       </c>
       <c r="I82" t="n">
         <v>1</v>
@@ -5254,32 +5475,35 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0.258</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0.582</v>
+        <v>0.4</v>
       </c>
       <c r="M82" t="n">
-        <v>0.007</v>
+        <v>0.4145549256663469</v>
       </c>
       <c r="N82" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="O82" t="inlineStr">
+        <v>0.04334272161126078</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.3608091395019315</v>
+      </c>
+      <c r="P82" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/111357087/</t>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111969683/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>idealista_110586470</t>
+          <t>idealista_109242406</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5289,21 +5513,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chalet adosado en Caneletes-Turonet, Cerdanyola del Vallès</t>
+          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>670000</v>
+        <v>570000</v>
       </c>
       <c r="E83" t="n">
-        <v>212</v>
+        <v>128</v>
       </c>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
@@ -5312,32 +5536,35 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0.628</v>
+        <v>0.25</v>
       </c>
       <c r="M83" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.4206198219841943</v>
       </c>
       <c r="N83" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.3447549515998395</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.3590682304537143</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110586470/</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/109242406/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>idealista_111572440</t>
+          <t>idealista_33799831</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5347,21 +5574,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Piso en Calle de Creu Casas i Sicart, 1, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Casa o chalet en Caneletes-Turonet, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>498000</v>
+        <v>675000</v>
       </c>
       <c r="E84" t="n">
-        <v>121</v>
+        <v>703</v>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
@@ -5370,32 +5597,35 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0.454</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0.411</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0.007</v>
+        <v>0.618819305761051</v>
       </c>
       <c r="N84" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.3382728162785832</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.3588396933418057</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111572440/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/33799831/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>idealista_111207597</t>
+          <t>idealista_101744285</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5405,23 +5635,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Piso en Rambla de Montserrat, 9, Fontetes, Cerdanyola del Vallès</t>
+          <t>Casa o chalet independiente en Calle de Felip II, Caneletes-Turonet, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>500000</v>
+        <v>675000</v>
       </c>
       <c r="E85" t="n">
-        <v>104</v>
+        <v>489</v>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
-      </c>
-      <c r="G85" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I85" t="n">
         <v>1</v>
@@ -5430,32 +5658,35 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0.391</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0.008</v>
+        <v>0.6140300983411522</v>
       </c>
       <c r="N85" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.3415568438190072</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.3573208303565117</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111207597/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/101744285/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>idealista_110926853</t>
+          <t>idealista_110659374</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5465,21 +5696,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Casa o chalet en Serraparera, Cerdanyola del Vallès</t>
+          <t>Piso en Calle de la Ciència, 5, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>495000</v>
+        <v>600000</v>
       </c>
       <c r="E86" t="n">
-        <v>103</v>
+        <v>161</v>
       </c>
       <c r="F86" t="n">
         <v>4</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I86" t="n">
         <v>1</v>
@@ -5488,32 +5719,35 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0.431</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0.421</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="M86" t="n">
-        <v>0.007</v>
+        <v>0.5311698316504831</v>
       </c>
       <c r="N86" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="O86" t="inlineStr">
+        <v>0.3430392067097512</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.3557418727800423</v>
+      </c>
+      <c r="P86" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/110926853/</t>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110659374/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>idealista_110912717</t>
+          <t>idealista_108639634</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5523,21 +5757,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Casa o chalet en Serraparera, Cerdanyola del Vallès</t>
+          <t>Casa o chalet en Calle de Pizarro, Caneletes-Turonet, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>495000</v>
+        <v>660000</v>
       </c>
       <c r="E87" t="n">
-        <v>103</v>
+        <v>291</v>
       </c>
       <c r="F87" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
@@ -5546,32 +5780,35 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0.431</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0.007</v>
+        <v>0.6094923420505066</v>
       </c>
       <c r="N87" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.3355734559961509</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.3545174645410122</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110912717/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/108639634/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>idealista_111009273</t>
+          <t>idealista_111786495</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5581,21 +5818,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chalet adosado en Serraparera, Cerdanyola del Vallès</t>
+          <t>Chalet adosado en Caneletes-Turonet, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>495000</v>
+        <v>675000</v>
       </c>
       <c r="E88" t="n">
-        <v>103</v>
+        <v>207</v>
       </c>
       <c r="F88" t="n">
         <v>4</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>0.02</v>
+        <v>26.05813735296297</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
@@ -5604,32 +5841,35 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0.431</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>0.007</v>
+        <v>0.6392067140646241</v>
       </c>
       <c r="N88" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.216688838836596</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.3491648082130082</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111009273/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111786495/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>idealista_33799831</t>
+          <t>idealista_111859088</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5639,21 +5879,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Casa o chalet en Caneletes-Turonet, Cerdanyola del Vallès</t>
+          <t>Casa o chalet independiente en Caneletes-Turonet, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>675000</v>
+        <v>599000</v>
       </c>
       <c r="E89" t="n">
-        <v>703</v>
+        <v>230</v>
       </c>
       <c r="F89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>0.02</v>
+        <v>17.12936420481481</v>
       </c>
       <c r="I89" t="n">
         <v>1</v>
@@ -5662,32 +5902,35 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0.61</v>
+        <v>0.105</v>
       </c>
       <c r="M89" t="n">
-        <v>0.006</v>
+        <v>0.5661093850596488</v>
       </c>
       <c r="N89" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.1527730449472502</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.3435265609475168</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/33799831/</t>
+          <t>within target band, strong size</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111859088/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>idealista_101744285</t>
+          <t>idealista_110719246</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5697,21 +5940,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Casa o chalet independiente en Calle de Felip II, Caneletes-Turonet, Cerdanyola del Vallès</t>
+          <t>Chalet adosado en Av Flor De Maig, Sant Ramón, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>675000</v>
+        <v>650000</v>
       </c>
       <c r="E90" t="n">
-        <v>489</v>
+        <v>217</v>
       </c>
       <c r="F90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I90" t="n">
         <v>1</v>
@@ -5720,32 +5963,35 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0.606</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>0.006</v>
+        <v>0.573893634055654</v>
       </c>
       <c r="N90" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="O90" t="inlineStr">
+        <v>0.3404552162999651</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.3402982712287461</v>
+      </c>
+      <c r="P90" t="inlineStr">
         <is>
           <t>near target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/101744285/</t>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110719246/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>idealista_111597228</t>
+          <t>idealista_111791864</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5755,21 +6001,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Piso en Calle de Creu Casas i Sicart, 1, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Casa o chalet independiente en Plaza Colón, Caneletes-Turonet, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>494000</v>
+        <v>675000</v>
       </c>
       <c r="E91" t="n">
-        <v>120</v>
+        <v>489</v>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>0.02</v>
+        <v>25.18991976037037</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -5778,32 +6024,35 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0.423</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0.411</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>0.007</v>
+        <v>0.6140300983411522</v>
       </c>
       <c r="N91" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.2278377242400143</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.3402629624196628</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111597228/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111791864/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>idealista_111602118</t>
+          <t>idealista_108314161</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5813,21 +6062,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chalet adosado en Caneletes-Turonet, Cerdanyola del Vallès</t>
+          <t>Casa o chalet en Ronda Serraparera, Serraparera, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>695000</v>
+        <v>615000</v>
       </c>
       <c r="E92" t="n">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="F92" t="n">
         <v>4</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -5836,32 +6085,35 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0.615</v>
+        <v>0.02499999999999998</v>
       </c>
       <c r="M92" t="n">
-        <v>0.005</v>
+        <v>0.5480735831627628</v>
       </c>
       <c r="N92" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="O92" t="inlineStr">
+        <v>0.3414207199500758</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.3378486754012485</v>
+      </c>
+      <c r="P92" t="inlineStr">
         <is>
           <t>near target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/111602118/</t>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/108314161/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>idealista_111531447</t>
+          <t>idealista_110271317</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5871,21 +6123,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Piso en Calle de Creu Casas i Sicart, 1, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Ático en Avenida de la Primavera, Martinica-Ateneu, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>488000</v>
+        <v>677500</v>
       </c>
       <c r="E93" t="n">
-        <v>120</v>
+        <v>242</v>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
@@ -5894,32 +6146,35 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0.376</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0.415</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>0.007</v>
+        <v>0.5630427286884008</v>
       </c>
       <c r="N93" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.3420162812195937</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.3359750507124442</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111531447/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110271317/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>idealista_111587545</t>
+          <t>idealista_111142454</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5929,21 +6184,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Piso en Calle de la Ciència, 5, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>486000</v>
+        <v>613000</v>
       </c>
       <c r="E94" t="n">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I94" t="n">
         <v>1</v>
@@ -5952,32 +6207,35 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0.425</v>
+        <v>0.03500000000000001</v>
       </c>
       <c r="M94" t="n">
-        <v>0.007</v>
+        <v>0.5313721925273804</v>
       </c>
       <c r="N94" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.3406743135044267</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.3340221303675406</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111587545/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111142454/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>idealista_110755540</t>
+          <t>idealista_111637945</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5987,21 +6245,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Piso en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
+          <t>Chalet adosado en Calle de les Vinyes, 3, Martinica-Ateneu, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>487000</v>
+        <v>635000</v>
       </c>
       <c r="E95" t="n">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I95" t="n">
         <v>1</v>
@@ -6010,32 +6268,35 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.368</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0.418</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0.007</v>
+        <v>0.5536466129485992</v>
       </c>
       <c r="N95" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.3391424656704126</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.3315976097693503</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110755540/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111637945/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>idealista_111003072</t>
+          <t>idealista_110575720</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6045,17 +6306,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chalet adosado en Calle Marqués de Comillas, 125, Zona Esportiva, Terrassa</t>
+          <t>Chalet adosado en Rd Cerdanyola, Caneletes-Turonet, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>494000</v>
-      </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
+        <v>650000</v>
+      </c>
+      <c r="E96" t="n">
+        <v>195</v>
+      </c>
+      <c r="F96" t="n">
+        <v>4</v>
+      </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I96" t="n">
         <v>1</v>
@@ -6064,32 +6329,35 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.423</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0.372</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0.006</v>
+        <v>0.5524045930346062</v>
       </c>
       <c r="N96" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>within target band</t>
-        </is>
+        <v>0.340916163035431</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.3313420160102261</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111003072/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110575720/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>idealista_111207233</t>
+          <t>idealista_111411842</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6099,23 +6367,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Piso en Rambla de Montserrat, 9, Fontetes, Cerdanyola del Vallès</t>
+          <t>Piso en Calle de la Ciència, 5, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>490000</v>
+        <v>616000</v>
       </c>
       <c r="E97" t="n">
-        <v>104</v>
+        <v>170</v>
       </c>
       <c r="F97" t="n">
-        <v>3</v>
-      </c>
-      <c r="G97" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I97" t="n">
         <v>1</v>
@@ -6124,32 +6390,35 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0.391</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0.394</v>
+        <v>0.01999999999999999</v>
       </c>
       <c r="M97" t="n">
-        <v>0.008</v>
+        <v>0.5296418799587156</v>
       </c>
       <c r="N97" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.3401975093616734</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.3282738784672883</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111207233/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111411842/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>idealista_110271317</t>
+          <t>idealista_111830289</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6159,21 +6428,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ático en Avenida de la Primavera, Martinica-Ateneu, Cerdanyola del Vallès</t>
+          <t>Chalet adosado en Calle Circular, Caneletes-Turonet, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>677500</v>
+        <v>605000</v>
       </c>
       <c r="E98" t="n">
-        <v>242</v>
+        <v>201</v>
       </c>
       <c r="F98" t="n">
         <v>4</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>0.02</v>
+        <v>18.17630864925926</v>
       </c>
       <c r="I98" t="n">
         <v>1</v>
@@ -6182,32 +6451,35 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0.173</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>0.551</v>
+        <v>0.075</v>
       </c>
       <c r="M98" t="n">
-        <v>0.007</v>
+        <v>0.5463083260156699</v>
       </c>
       <c r="N98" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="O98" t="inlineStr">
+        <v>0.1625856796457428</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.3267820113538196</v>
+      </c>
+      <c r="P98" t="inlineStr">
         <is>
           <t>near target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/110271317/</t>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111830289/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>idealista_111411017</t>
+          <t>idealista_110833654</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6217,21 +6489,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chalet adosado en Sant Ramón, Cerdanyola del Vallès</t>
+          <t>Chalet pareado en Avenida de Canaletes, Caneletes-Turonet, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>680000</v>
+        <v>625000</v>
       </c>
       <c r="E99" t="n">
-        <v>203</v>
+        <v>170</v>
       </c>
       <c r="F99" t="n">
         <v>5</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I99" t="n">
         <v>1</v>
@@ -6240,32 +6512,35 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0.166</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0.529</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>0.006</v>
+        <v>0.5422593661313356</v>
       </c>
       <c r="N99" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>near target band, strong size</t>
-        </is>
+        <v>0.3384566378845031</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.3267120919382132</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111411017/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110833654/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>idealista_111207022</t>
+          <t>idealista_111411017</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6275,23 +6550,21 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Piso en Rambla de Montserrat, 9, Fontetes, Cerdanyola del Vallès</t>
+          <t>Chalet adosado en Sant Ramón, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>650000</v>
+        <v>680000</v>
       </c>
       <c r="E100" t="n">
-        <v>105</v>
+        <v>203</v>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
-      </c>
-      <c r="G100" t="n">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I100" t="n">
         <v>1</v>
@@ -6300,32 +6573,35 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0.351</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>0.384</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>0.007</v>
+        <v>0.5403255808128237</v>
       </c>
       <c r="N100" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.3390725751396857</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.3259922926927156</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111207022/</t>
+          <t>near target band, strong size</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111411017/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>idealista_109937600</t>
+          <t>idealista_110324575</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6335,21 +6611,21 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Casa de pueblo en Sant Ramón, Cerdanyola del Vallès</t>
+          <t>Ático en Calle De Creu Casas i Sicart s/n, Parc d'Alba, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>670000</v>
+        <v>589000</v>
       </c>
       <c r="E101" t="n">
-        <v>370</v>
+        <v>122</v>
       </c>
       <c r="F101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>0.02</v>
+        <v>37.07040587148148</v>
       </c>
       <c r="I101" t="n">
         <v>1</v>
@@ -6358,25 +6634,28 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0.476</v>
+        <v>0.155</v>
       </c>
       <c r="M101" t="n">
-        <v>0.005</v>
+        <v>0.4025085235019009</v>
       </c>
       <c r="N101" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.339990340266814</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.3193967933911972</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/109937600/</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110324575/</t>
         </is>
       </c>
     </row>
